--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122574699</v>
+        <v>122574697</v>
       </c>
       <c r="B2" t="n">
         <v>79274</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607186</v>
+        <v>607217</v>
       </c>
       <c r="R2" t="n">
-        <v>6749813</v>
+        <v>6749865</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122574695</v>
+        <v>122574699</v>
       </c>
       <c r="B3" t="n">
         <v>79274</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607230</v>
+        <v>607186</v>
       </c>
       <c r="R3" t="n">
-        <v>6749843</v>
+        <v>6749813</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122574697</v>
+        <v>122574695</v>
       </c>
       <c r="B4" t="n">
         <v>79274</v>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607217</v>
+        <v>607230</v>
       </c>
       <c r="R4" t="n">
-        <v>6749865</v>
+        <v>6749843</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122574699</v>
+        <v>122574695</v>
       </c>
       <c r="B3" t="n">
         <v>79274</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607186</v>
+        <v>607230</v>
       </c>
       <c r="R3" t="n">
-        <v>6749813</v>
+        <v>6749843</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122574695</v>
+        <v>122574699</v>
       </c>
       <c r="B4" t="n">
         <v>79274</v>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607230</v>
+        <v>607186</v>
       </c>
       <c r="R4" t="n">
-        <v>6749843</v>
+        <v>6749813</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122574695</v>
+        <v>122574699</v>
       </c>
       <c r="B3" t="n">
         <v>79274</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607230</v>
+        <v>607186</v>
       </c>
       <c r="R3" t="n">
-        <v>6749843</v>
+        <v>6749813</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122574699</v>
+        <v>122574695</v>
       </c>
       <c r="B4" t="n">
         <v>79274</v>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607186</v>
+        <v>607230</v>
       </c>
       <c r="R4" t="n">
-        <v>6749813</v>
+        <v>6749843</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122574697</v>
+        <v>122574699</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607217</v>
+        <v>607186</v>
       </c>
       <c r="R2" t="n">
-        <v>6749865</v>
+        <v>6749813</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122574699</v>
+        <v>122574697</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607186</v>
+        <v>607217</v>
       </c>
       <c r="R3" t="n">
-        <v>6749813</v>
+        <v>6749865</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
         <v>122574695</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>79275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122574699</v>
+        <v>122574695</v>
       </c>
       <c r="B2" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607186</v>
+        <v>607230</v>
       </c>
       <c r="R2" t="n">
-        <v>6749813</v>
+        <v>6749843</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,7 +803,7 @@
         <v>122574697</v>
       </c>
       <c r="B3" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122574695</v>
+        <v>122574699</v>
       </c>
       <c r="B4" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607230</v>
+        <v>607186</v>
       </c>
       <c r="R4" t="n">
-        <v>6749843</v>
+        <v>6749813</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122574695</v>
+        <v>122574699</v>
       </c>
       <c r="B2" t="n">
         <v>79278</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607230</v>
+        <v>607186</v>
       </c>
       <c r="R2" t="n">
-        <v>6749843</v>
+        <v>6749813</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122574699</v>
+        <v>122574695</v>
       </c>
       <c r="B4" t="n">
         <v>79278</v>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607186</v>
+        <v>607230</v>
       </c>
       <c r="R4" t="n">
-        <v>6749813</v>
+        <v>6749843</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122574697</v>
+        <v>122574699</v>
       </c>
       <c r="B2" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607217</v>
+        <v>607186</v>
       </c>
       <c r="R2" t="n">
-        <v>6749865</v>
+        <v>6749813</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122574699</v>
+        <v>122574695</v>
       </c>
       <c r="B3" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607186</v>
+        <v>607230</v>
       </c>
       <c r="R3" t="n">
-        <v>6749813</v>
+        <v>6749843</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122574695</v>
+        <v>122574697</v>
       </c>
       <c r="B4" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607230</v>
+        <v>607217</v>
       </c>
       <c r="R4" t="n">
-        <v>6749843</v>
+        <v>6749865</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122574699</v>
+        <v>122574697</v>
       </c>
       <c r="B2" t="n">
         <v>79384</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607186</v>
+        <v>607217</v>
       </c>
       <c r="R2" t="n">
-        <v>6749813</v>
+        <v>6749865</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122574697</v>
+        <v>122574699</v>
       </c>
       <c r="B4" t="n">
         <v>79384</v>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607217</v>
+        <v>607186</v>
       </c>
       <c r="R4" t="n">
-        <v>6749865</v>
+        <v>6749813</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122574697</v>
+        <v>122574695</v>
       </c>
       <c r="B2" t="n">
         <v>79384</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607217</v>
+        <v>607230</v>
       </c>
       <c r="R2" t="n">
-        <v>6749865</v>
+        <v>6749843</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122574695</v>
+        <v>122574697</v>
       </c>
       <c r="B3" t="n">
         <v>79384</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607230</v>
+        <v>607217</v>
       </c>
       <c r="R3" t="n">
-        <v>6749843</v>
+        <v>6749865</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122574695</v>
+        <v>122574699</v>
       </c>
       <c r="B2" t="n">
         <v>79384</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607230</v>
+        <v>607186</v>
       </c>
       <c r="R2" t="n">
-        <v>6749843</v>
+        <v>6749813</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122574697</v>
+        <v>122574695</v>
       </c>
       <c r="B3" t="n">
         <v>79384</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607217</v>
+        <v>607230</v>
       </c>
       <c r="R3" t="n">
-        <v>6749865</v>
+        <v>6749843</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122574699</v>
+        <v>122574697</v>
       </c>
       <c r="B4" t="n">
         <v>79384</v>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607186</v>
+        <v>607217</v>
       </c>
       <c r="R4" t="n">
-        <v>6749813</v>
+        <v>6749865</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122574695</v>
+        <v>122574697</v>
       </c>
       <c r="B3" t="n">
         <v>79384</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607230</v>
+        <v>607217</v>
       </c>
       <c r="R3" t="n">
-        <v>6749843</v>
+        <v>6749865</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122574697</v>
+        <v>122574695</v>
       </c>
       <c r="B4" t="n">
         <v>79384</v>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607217</v>
+        <v>607230</v>
       </c>
       <c r="R4" t="n">
-        <v>6749865</v>
+        <v>6749843</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,136 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Stora Enso - NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123321748</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hagsta, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607131</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6749839</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_189</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>123321748</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>123321748</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>123321748</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4234-2025 artfynd.xlsx
+++ b/artfynd/A 4234-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>123321748</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
